--- a/artfynd/A 35783-2025 artfynd.xlsx
+++ b/artfynd/A 35783-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5058245</v>
+        <v>137164422</v>
       </c>
       <c r="B2" t="n">
-        <v>101326</v>
+        <v>30306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>200985</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lundskog nordost Rågårdsdal, Boh</t>
+          <t>Bastevik, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>291001</v>
+        <v>290642</v>
       </c>
       <c r="R2" t="n">
-        <v>6479058</v>
+        <v>6479275</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +745,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1995-07-11</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1995-07-11</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Bro, Skog</t>
+          <t>Under grova hyggesrester av al</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,27 +780,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Flora Bohuslän</t>
+          <t>Erik Börjesson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Flora Bohuslän</t>
+          <t>Erik Börjesson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5058245</t>
+          <t>https://artportalen.se/Sighting/137164422</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5230259</v>
+        <v>5058245</v>
       </c>
       <c r="B3" t="n">
-        <v>101228</v>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -887,6 +897,113 @@
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5058245</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5230259</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lundskog nordost Rågårdsdal, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>291001</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6479058</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lysekil</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bro</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1995-07-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1995-07-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bro, Skog</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Flora Bohuslän</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Flora Bohuslän</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/5230259</t>
         </is>
@@ -896,6 +1013,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35783-2025 artfynd.xlsx
+++ b/artfynd/A 35783-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137164422</v>
       </c>
       <c r="B2" t="n">
-        <v>30306</v>
+        <v>30319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35783-2025 artfynd.xlsx
+++ b/artfynd/A 35783-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137164422</v>
       </c>
       <c r="B2" t="n">
-        <v>30319</v>
+        <v>30321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35783-2025 artfynd.xlsx
+++ b/artfynd/A 35783-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137164422</v>
       </c>
       <c r="B2" t="n">
-        <v>30321</v>
+        <v>30331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35783-2025 artfynd.xlsx
+++ b/artfynd/A 35783-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137164422</v>
       </c>
       <c r="B2" t="n">
-        <v>30331</v>
+        <v>30332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
